--- a/output/pdf_financials_xlsx/HWO.xlsx
+++ b/output/pdf_financials_xlsx/HWO.xlsx
@@ -927,7 +927,7 @@
         <v>0.0001219</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.0001365</v>
+        <v>0.0001367</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.0001644</v>
@@ -89532,7 +89532,7 @@
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">

--- a/output/pdf_financials_xlsx/HWO.xlsx
+++ b/output/pdf_financials_xlsx/HWO.xlsx
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>1.37e-05</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>1.3e-06</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>8.1e-06</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -68440,7 +68440,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E636" s="5" t="n">
         <v>1.37e-05</v>
       </c>
@@ -69384,7 +69388,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D646" t="inlineStr"/>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E646" t="inlineStr">
         <is>
           <t>-</t>
@@ -71876,7 +71884,11 @@
           <t>Proceeds on sales of property and equipment</t>
         </is>
       </c>
-      <c r="D672" t="inlineStr"/>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E672" s="5" t="n">
         <v>1.88e-05</v>
       </c>
